--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="service_charge_history" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="151">
   <si>
     <t>TC ID</t>
   </si>
@@ -103,10 +104,16 @@
     <t>3. Read the page &lt;h1&gt; text</t>
   </si>
   <si>
-    <t>The heading reflects the currently selected office name (e.g. `Service Charge — Parker Palm Springs`).</t>
-  </si>
-  <si>
-    <t>4. Read the four column header texts in order</t>
+    <t>The heading reads `Service Charge` (same on both tabs; office context is not in the h1).</t>
+  </si>
+  <si>
+    <t>4. Read the History section header</t>
+  </si>
+  <si>
+    <t>The header reads `Service Charge History : Parker Palm Springs` — office name is present.</t>
+  </si>
+  <si>
+    <t>5. Read the four column header texts in order</t>
   </si>
   <si>
     <t>The headers are `Service Type`, `Service Charge Percentage`, `Modified By`, `Modified On` — verbatim, in that order.</t>
@@ -291,7 +298,7 @@
     <t>TC-SVC-HIS-010</t>
   </si>
   <si>
-    <t>Modified By cells render a raw GUID, not a person name or email</t>
+    <t>Modified By cells render a user identifier, not a raw GUID</t>
   </si>
   <si>
     <t>1. Read the Modified By cell text for the first row</t>
@@ -429,7 +436,7 @@
     <t>2. Click the "Service Charge History" tab without saving</t>
   </si>
   <si>
-    <t>An Unsaved Changes confirmation modal appears with Save Changes, Discard Changes, and Cancel options. The application does not navigate to the History tab without user confirmation.</t>
+    <t>An "Unsaved changes" modal appears with **Stay** and **Discard** buttons. The application does not navigate to the History tab without user confirmation.</t>
   </si>
   <si>
     <t>TC-SVC-HIS-015</t>
@@ -468,7 +475,10 @@
     <t>Pass:15 Fail:0 Skipped:0 Blocked:0</t>
   </si>
   <si>
-    <t>Last Updated: 2026-08-11</t>
+    <t>Last Updated: 2026-08-14</t>
+  </si>
+  <si>
+    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
   </si>
 </sst>
 </file>
@@ -857,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1079,40 +1089,40 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="L6" t="s">
         <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" t="s">
-        <v>37</v>
       </c>
       <c r="M6" t="s">
         <v>25</v>
@@ -1120,34 +1130,34 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K7" t="s">
         <v>38</v>
@@ -1161,40 +1171,40 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" t="s">
         <v>40</v>
       </c>
-      <c r="B8" t="s">
+      <c r="L8" t="s">
         <v>41</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" t="s">
-        <v>45</v>
       </c>
       <c r="M8" t="s">
         <v>25</v>
@@ -1202,34 +1212,34 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K9" t="s">
         <v>46</v>
@@ -1243,40 +1253,40 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" t="s">
         <v>48</v>
       </c>
-      <c r="B10" t="s">
+      <c r="L10" t="s">
         <v>49</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K10" t="s">
-        <v>51</v>
-      </c>
-      <c r="L10" t="s">
-        <v>52</v>
       </c>
       <c r="M10" t="s">
         <v>25</v>
@@ -1284,34 +1294,34 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="K11" t="s">
         <v>53</v>
@@ -1325,40 +1335,40 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" t="s">
         <v>55</v>
       </c>
-      <c r="B12" t="s">
+      <c r="L12" t="s">
         <v>56</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K12" t="s">
-        <v>57</v>
-      </c>
-      <c r="L12" t="s">
-        <v>58</v>
       </c>
       <c r="M12" t="s">
         <v>25</v>
@@ -1366,34 +1376,34 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="K13" t="s">
         <v>59</v>
@@ -1407,40 +1417,40 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" t="s">
         <v>61</v>
       </c>
-      <c r="B14" t="s">
+      <c r="L14" t="s">
         <v>62</v>
-      </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" t="s">
-        <v>63</v>
-      </c>
-      <c r="K14" t="s">
-        <v>64</v>
-      </c>
-      <c r="L14" t="s">
-        <v>65</v>
       </c>
       <c r="M14" t="s">
         <v>25</v>
@@ -1448,34 +1458,34 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="K15" t="s">
         <v>66</v>
@@ -1530,40 +1540,40 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" t="s">
         <v>70</v>
       </c>
-      <c r="B17" t="s">
+      <c r="L17" t="s">
         <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" t="s">
-        <v>50</v>
-      </c>
-      <c r="K17" t="s">
-        <v>72</v>
-      </c>
-      <c r="L17" t="s">
-        <v>73</v>
       </c>
       <c r="M17" t="s">
         <v>25</v>
@@ -1571,10 +1581,10 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
@@ -1583,7 +1593,7 @@
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -1598,13 +1608,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="M18" t="s">
         <v>25</v>
@@ -1612,34 +1622,34 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H19" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J19" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="K19" t="s">
         <v>79</v>
@@ -1653,40 +1663,40 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" t="s">
         <v>81</v>
       </c>
-      <c r="B20" t="s">
+      <c r="L20" t="s">
         <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" t="s">
-        <v>83</v>
-      </c>
-      <c r="K20" t="s">
-        <v>84</v>
-      </c>
-      <c r="L20" t="s">
-        <v>85</v>
       </c>
       <c r="M20" t="s">
         <v>25</v>
@@ -1694,34 +1704,34 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H21" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J21" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="K21" t="s">
         <v>86</v>
@@ -1735,40 +1745,40 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" t="s">
+        <v>25</v>
+      </c>
+      <c r="J22" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" t="s">
         <v>88</v>
       </c>
-      <c r="B22" t="s">
+      <c r="L22" t="s">
         <v>89</v>
-      </c>
-      <c r="C22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" t="s">
-        <v>50</v>
-      </c>
-      <c r="K22" t="s">
-        <v>90</v>
-      </c>
-      <c r="L22" t="s">
-        <v>91</v>
       </c>
       <c r="M22" t="s">
         <v>25</v>
@@ -1776,34 +1786,34 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H23" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I23" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="K23" t="s">
         <v>92</v>
@@ -1817,40 +1827,40 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I24" t="s">
+        <v>25</v>
+      </c>
+      <c r="J24" t="s">
+        <v>25</v>
+      </c>
+      <c r="K24" t="s">
         <v>94</v>
       </c>
-      <c r="B24" t="s">
+      <c r="L24" t="s">
         <v>95</v>
-      </c>
-      <c r="C24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" t="s">
-        <v>96</v>
-      </c>
-      <c r="K24" t="s">
-        <v>97</v>
-      </c>
-      <c r="L24" t="s">
-        <v>98</v>
       </c>
       <c r="M24" t="s">
         <v>25</v>
@@ -1858,34 +1868,34 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G25" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I25" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="K25" t="s">
         <v>99</v>
@@ -1981,40 +1991,40 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28" t="s">
         <v>105</v>
       </c>
-      <c r="B28" t="s">
+      <c r="L28" t="s">
         <v>106</v>
-      </c>
-      <c r="C28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" t="s">
-        <v>107</v>
-      </c>
-      <c r="F28" t="s">
-        <v>18</v>
-      </c>
-      <c r="G28" t="s">
-        <v>19</v>
-      </c>
-      <c r="H28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I28" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" t="s">
-        <v>50</v>
-      </c>
-      <c r="K28" t="s">
-        <v>108</v>
-      </c>
-      <c r="L28" t="s">
-        <v>109</v>
       </c>
       <c r="M28" t="s">
         <v>25</v>
@@ -2022,34 +2032,34 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="F29" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G29" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H29" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="K29" t="s">
         <v>110</v>
@@ -2104,40 +2114,40 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" t="s">
+        <v>25</v>
+      </c>
+      <c r="I31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" t="s">
         <v>114</v>
       </c>
-      <c r="B31" t="s">
+      <c r="L31" t="s">
         <v>115</v>
-      </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" t="s">
-        <v>42</v>
-      </c>
-      <c r="F31" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" t="s">
-        <v>19</v>
-      </c>
-      <c r="H31" t="s">
-        <v>20</v>
-      </c>
-      <c r="I31" t="s">
-        <v>21</v>
-      </c>
-      <c r="J31" t="s">
-        <v>116</v>
-      </c>
-      <c r="K31" t="s">
-        <v>117</v>
-      </c>
-      <c r="L31" t="s">
-        <v>118</v>
       </c>
       <c r="M31" t="s">
         <v>25</v>
@@ -2145,34 +2155,34 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G32" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H32" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="K32" t="s">
         <v>119</v>
@@ -2350,40 +2360,40 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" t="s">
+        <v>25</v>
+      </c>
+      <c r="I37" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" t="s">
         <v>129</v>
       </c>
-      <c r="B37" t="s">
+      <c r="L37" t="s">
         <v>130</v>
-      </c>
-      <c r="C37" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" t="s">
-        <v>21</v>
-      </c>
-      <c r="J37" t="s">
-        <v>22</v>
-      </c>
-      <c r="K37" t="s">
-        <v>131</v>
-      </c>
-      <c r="L37" t="s">
-        <v>132</v>
       </c>
       <c r="M37" t="s">
         <v>25</v>
@@ -2391,34 +2401,34 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G38" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H38" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J38" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K38" t="s">
         <v>133</v>
@@ -2432,40 +2442,40 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" t="s">
+        <v>25</v>
+      </c>
+      <c r="I39" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" t="s">
+        <v>25</v>
+      </c>
+      <c r="K39" t="s">
         <v>135</v>
       </c>
-      <c r="B39" t="s">
+      <c r="L39" t="s">
         <v>136</v>
-      </c>
-      <c r="C39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" t="s">
-        <v>16</v>
-      </c>
-      <c r="E39" t="s">
-        <v>17</v>
-      </c>
-      <c r="F39" t="s">
-        <v>18</v>
-      </c>
-      <c r="G39" t="s">
-        <v>19</v>
-      </c>
-      <c r="H39" t="s">
-        <v>20</v>
-      </c>
-      <c r="I39" t="s">
-        <v>21</v>
-      </c>
-      <c r="J39" t="s">
-        <v>137</v>
-      </c>
-      <c r="K39" t="s">
-        <v>138</v>
-      </c>
-      <c r="L39" t="s">
-        <v>139</v>
       </c>
       <c r="M39" t="s">
         <v>25</v>
@@ -2473,40 +2483,40 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G40" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H40" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J40" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="K40" t="s">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="L40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M40" t="s">
         <v>25</v>
@@ -2544,7 +2554,7 @@
         <v>25</v>
       </c>
       <c r="K41" t="s">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="L41" t="s">
         <v>142</v>
@@ -2553,45 +2563,102 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" t="s">
+        <v>25</v>
+      </c>
+      <c r="H42" t="s">
+        <v>25</v>
+      </c>
+      <c r="I42" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" t="s">
         <v>143</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="L42" t="s">
         <v>144</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H43" s="2" t="s">
+      <c r="M42" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="I43" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="J43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M43" s="2" t="s">
+      <c r="C44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>147</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="156">
   <si>
     <t>TC ID</t>
   </si>
@@ -349,31 +349,48 @@
     <t>TC-SVC-HIS-012</t>
   </si>
   <si>
-    <t>Clicking a column header does not set on the header</t>
+    <t>Sorting the History grid by Modified On via the column header dropdown reorders rows</t>
   </si>
   <si>
     <t xml:space="preserve">User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Service Type"</t>
-  </si>
-  <si>
-    <t>1. Record the first row's content</t>
-  </si>
-  <si>
-    <t>Row 0 shows the most recent record</t>
-  </si>
-  <si>
-    <t>2. Click the "Service Type" column header button</t>
-  </si>
-  <si>
-    <t>No row reorder occurs; the first row remains unchanged</t>
-  </si>
-  <si>
-    <t>3. Check the attribute on the Service Type column header</t>
-  </si>
-  <si>
-    <t>`aria-sort` is not set — the header does not expose a sort affordance</t>
+Sample input 1: "Modified On"
+Sample input 2: "Sort ascending"
+Sample input 3: "Sort descending"</t>
+  </si>
+  <si>
+    <t>The History grid for office 1604 is fully loaded (at least 2 rows)</t>
+  </si>
+  <si>
+    <t>1. Click the "Modified On" column header to open its dropdown</t>
+  </si>
+  <si>
+    <t>A menu appears with "Sort ascending", "Sort descending", and "Hide column" items</t>
+  </si>
+  <si>
+    <t>2. Click "Sort ascending" and wait for the grid to re-render</t>
+  </si>
+  <si>
+    <t>Row 0 now shows the oldest record</t>
+  </si>
+  <si>
+    <t>3. Assert that row 0's Modified On date equals the minimum date of all visible rows</t>
+  </si>
+  <si>
+    <t>Ascending row 0 carries the minimum visible date</t>
+  </si>
+  <si>
+    <t>4. Click the "Modified On" column header again and click "Sort descending"</t>
+  </si>
+  <si>
+    <t>Row 0 now shows the most recent record</t>
+  </si>
+  <si>
+    <t>5. Assert that descending row 0 differs from ascending row 0</t>
+  </si>
+  <si>
+    <t>The two row 0 values are not equal, proving the grid reordered</t>
   </si>
   <si>
     <t>TC-SVC-HIS-013</t>
@@ -475,10 +492,10 @@
     <t>Pass:15 Fail:0 Skipped:0 Blocked:0</t>
   </si>
   <si>
-    <t>Last Updated: 2026-08-14</t>
-  </si>
-  <si>
-    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
+    <t>Last Updated: 2026-08-16</t>
+  </si>
+  <si>
+    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
   </si>
 </sst>
 </file>
@@ -867,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2059,13 +2076,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="K29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M29" t="s">
         <v>25</v>
@@ -2103,10 +2120,10 @@
         <v>25</v>
       </c>
       <c r="K30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M30" t="s">
         <v>25</v>
@@ -2144,10 +2161,10 @@
         <v>25</v>
       </c>
       <c r="K31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M31" t="s">
         <v>25</v>
@@ -2155,40 +2172,40 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" t="s">
+        <v>25</v>
+      </c>
+      <c r="I32" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" t="s">
         <v>117</v>
       </c>
-      <c r="C32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" t="s">
-        <v>20</v>
-      </c>
-      <c r="I32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J32" t="s">
+      <c r="L32" t="s">
         <v>118</v>
-      </c>
-      <c r="K32" t="s">
-        <v>119</v>
-      </c>
-      <c r="L32" t="s">
-        <v>120</v>
       </c>
       <c r="M32" t="s">
         <v>25</v>
@@ -2226,10 +2243,10 @@
         <v>25</v>
       </c>
       <c r="K33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L33" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M33" t="s">
         <v>25</v>
@@ -2237,40 +2254,40 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E34" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F34" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G34" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="K34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M34" t="s">
         <v>25</v>
@@ -2308,10 +2325,10 @@
         <v>25</v>
       </c>
       <c r="K35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M35" t="s">
         <v>25</v>
@@ -2349,10 +2366,10 @@
         <v>25</v>
       </c>
       <c r="K36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M36" t="s">
         <v>25</v>
@@ -2390,10 +2407,10 @@
         <v>25</v>
       </c>
       <c r="K37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M37" t="s">
         <v>25</v>
@@ -2401,40 +2418,40 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" t="s">
+        <v>25</v>
+      </c>
+      <c r="I38" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" t="s">
         <v>132</v>
       </c>
-      <c r="C38" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" t="s">
-        <v>16</v>
-      </c>
-      <c r="E38" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38" t="s">
-        <v>19</v>
-      </c>
-      <c r="H38" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" t="s">
-        <v>21</v>
-      </c>
-      <c r="J38" t="s">
-        <v>22</v>
-      </c>
-      <c r="K38" t="s">
+      <c r="L38" t="s">
         <v>133</v>
-      </c>
-      <c r="L38" t="s">
-        <v>134</v>
       </c>
       <c r="M38" t="s">
         <v>25</v>
@@ -2472,10 +2489,10 @@
         <v>25</v>
       </c>
       <c r="K39" t="s">
+        <v>134</v>
+      </c>
+      <c r="L39" t="s">
         <v>135</v>
-      </c>
-      <c r="L39" t="s">
-        <v>136</v>
       </c>
       <c r="M39" t="s">
         <v>25</v>
@@ -2483,10 +2500,10 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" t="s">
         <v>137</v>
-      </c>
-      <c r="B40" t="s">
-        <v>138</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
@@ -2510,13 +2527,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" t="s">
+        <v>138</v>
+      </c>
+      <c r="L40" t="s">
         <v>139</v>
-      </c>
-      <c r="K40" t="s">
-        <v>140</v>
-      </c>
-      <c r="L40" t="s">
-        <v>141</v>
       </c>
       <c r="M40" t="s">
         <v>25</v>
@@ -2554,10 +2571,10 @@
         <v>25</v>
       </c>
       <c r="K41" t="s">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="L41" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M41" t="s">
         <v>25</v>
@@ -2565,84 +2582,166 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="B42" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H42" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="K42" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L42" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M42" t="s">
         <v>25</v>
       </c>
     </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" t="s">
+        <v>25</v>
+      </c>
+      <c r="H43" t="s">
+        <v>25</v>
+      </c>
+      <c r="I43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" t="s">
+        <v>147</v>
+      </c>
+      <c r="M43" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I44" s="2" t="s">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44" t="s">
+        <v>25</v>
+      </c>
+      <c r="H44" t="s">
+        <v>25</v>
+      </c>
+      <c r="I44" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" t="s">
+        <v>25</v>
+      </c>
+      <c r="K44" t="s">
         <v>148</v>
       </c>
-      <c r="J44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M44" s="2" t="s">
+      <c r="L44" t="s">
         <v>149</v>
+      </c>
+      <c r="M44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2658,7 +2757,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -495,7 +495,7 @@
     <t>Last Updated: 2026-08-16</t>
   </si>
   <si>
-    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
+    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -495,7 +495,7 @@
     <t>Last Updated: 2026-08-16</t>
   </si>
   <si>
-    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
+    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -495,7 +495,7 @@
     <t>Last Updated: 2026-08-16</t>
   </si>
   <si>
-    <t>f9d696e3767564ce556785ab32c8d4d620422045a781f574890b1a82aec41d64</t>
+    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -495,7 +495,7 @@
     <t>Last Updated: 2026-08-16</t>
   </si>
   <si>
-    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
+    <t>e654a4f812c4ac1bbbd49bec0a6a66cc601c73fe4374e6e441effe43a9071f32</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -495,7 +495,7 @@
     <t>Last Updated: 2026-08-16</t>
   </si>
   <si>
-    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
+    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -495,7 +495,7 @@
     <t>Last Updated: 2026-08-16</t>
   </si>
   <si>
-    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
+    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -495,7 +495,7 @@
     <t>Last Updated: 2026-08-16</t>
   </si>
   <si>
-    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
+    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -495,7 +495,7 @@
     <t>Last Updated: 2026-08-16</t>
   </si>
   <si>
-    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
+    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -495,7 +495,7 @@
     <t>Last Updated: 2026-08-16</t>
   </si>
   <si>
-    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
+    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -495,7 +495,7 @@
     <t>Last Updated: 2026-08-16</t>
   </si>
   <si>
-    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
+    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -495,7 +495,7 @@
     <t>Last Updated: 2026-08-16</t>
   </si>
   <si>
-    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
+    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -495,7 +495,7 @@
     <t>Last Updated: 2026-08-16</t>
   </si>
   <si>
-    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
+    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/service-charge/service-charge-history.xlsx
+++ b/clients/encore/testcases/service-charge/service-charge-history.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="service_charge_history" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="155">
   <si>
     <t>TC ID</t>
   </si>
@@ -493,9 +492,6 @@
   </si>
   <si>
     <t>Last Updated: 2026-08-16</t>
-  </si>
-  <si>
-    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>
@@ -2748,20 +2744,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>